--- a/jpcore-r4/main/StructureDefinition-jp-observation-microbiology.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-microbiology.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4444" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4445" uniqueCount="602">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,7 +90,8 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright JED-Project、JAHIS、日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG  
+This material contains content from LOINC (http://loinc.org). LOINC is copyright © 1995+, Regenstrief Institute, Inc. and the Logical Observation Identifiers Names and Codes (LOINC) Committee and is available at no cost under the license at http://loinc.org/license. LOINC® is a registered United States trademark of Regenstrief Institute, Inc</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -329,16 +330,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -464,7 +465,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -621,7 +622,10 @@
     <t>どの観測値が取得されて表示されるかをフィルタリングするために使用されます。 / Used for filtering what observations are retrieved and displayed.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
+    <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -637,19 +641,22 @@
     <t>FiveWs.class</t>
   </si>
   <si>
-    <t>Observation.category:laboratory</t>
-  </si>
-  <si>
-    <t>laboratory</t>
+    <t>Observation.category:first</t>
+  </si>
+  <si>
+    <t>first</t>
   </si>
   <si>
     <t>このObservationに関する分類（JP_SimpleObservationCategory_VS）、必須項目</t>
   </si>
   <si>
-    <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
-  </si>
-  <si>
-    <t>Observation.category:laboratory.id</t>
+    <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
+  </si>
+  <si>
+    <t>Observation.category:first.id</t>
   </si>
   <si>
     <t>Observation.category.id</t>
@@ -671,7 +678,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>Observation.category:laboratory.extension</t>
+    <t>Observation.category:first.extension</t>
   </si>
   <si>
     <t>Observation.category.extension</t>
@@ -690,7 +697,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>Observation.category:laboratory.coding</t>
+    <t>Observation.category:first.coding</t>
   </si>
   <si>
     <t>Observation.category.coding</t>
@@ -721,19 +728,19 @@
     <t>union(., ./translation)</t>
   </si>
   <si>
-    <t>Observation.category:laboratory.coding.id</t>
+    <t>Observation.category:first.coding.id</t>
   </si>
   <si>
     <t>Observation.category.coding.id</t>
   </si>
   <si>
-    <t>Observation.category:laboratory.coding.extension</t>
+    <t>Observation.category:first.coding.extension</t>
   </si>
   <si>
     <t>Observation.category.coding.extension</t>
   </si>
   <si>
-    <t>Observation.category:laboratory.coding.system</t>
+    <t>Observation.category:first.coding.system</t>
   </si>
   <si>
     <t>Observation.category.coding.system</t>
@@ -763,7 +770,7 @@
     <t>./codeSystem</t>
   </si>
   <si>
-    <t>Observation.category:laboratory.coding.version</t>
+    <t>Observation.category:first.coding.version</t>
   </si>
   <si>
     <t>Observation.category.coding.version</t>
@@ -787,7 +794,7 @@
     <t>./codeSystemVersion</t>
   </si>
   <si>
-    <t>Observation.category:laboratory.coding.code</t>
+    <t>Observation.category:first.coding.code</t>
   </si>
   <si>
     <t>Observation.category.coding.code</t>
@@ -802,6 +809,9 @@
     <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
   </si>
   <si>
+    <t>laboratory</t>
+  </si>
+  <si>
     <t>Coding.code</t>
   </si>
   <si>
@@ -811,7 +821,7 @@
     <t>./code</t>
   </si>
   <si>
-    <t>Observation.category:laboratory.coding.display</t>
+    <t>Observation.category:first.coding.display</t>
   </si>
   <si>
     <t>Observation.category.coding.display</t>
@@ -835,7 +845,7 @@
     <t>CV.displayName</t>
   </si>
   <si>
-    <t>Observation.category:laboratory.coding.userSelected</t>
+    <t>Observation.category:first.coding.userSelected</t>
   </si>
   <si>
     <t>Observation.category.coding.userSelected</t>
@@ -866,7 +876,7 @@
     <t>CD.codingRationale</t>
   </si>
   <si>
-    <t>Observation.category:laboratory.text</t>
+    <t>Observation.category:first.text</t>
   </si>
   <si>
     <t>Observation.category.text</t>
@@ -893,64 +903,64 @@
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
-    <t>Observation.category:microbiology</t>
-  </si>
-  <si>
-    <t>microbiology</t>
-  </si>
-  <si>
-    <t>このObservationに関するLOINC上の分類、任意項目</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationCategory_Microbiology_VS</t>
-  </si>
-  <si>
-    <t>Observation.category:microbiology.id</t>
-  </si>
-  <si>
-    <t>Observation.category:microbiology.extension</t>
-  </si>
-  <si>
-    <t>Observation.category:microbiology.coding</t>
-  </si>
-  <si>
-    <t>Observation.category:microbiology.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.category:microbiology.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.category:microbiology.coding.system</t>
+    <t>Observation.category:second</t>
+  </si>
+  <si>
+    <t>second</t>
+  </si>
+  <si>
+    <t>第2カテゴリはLOINCのコード18725-2固定とする、ValueSetは指定しない</t>
+  </si>
+  <si>
+    <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
+  </si>
+  <si>
+    <t>Observation.category:second.id</t>
+  </si>
+  <si>
+    <t>Observation.category:second.extension</t>
+  </si>
+  <si>
+    <t>Observation.category:second.coding</t>
+  </si>
+  <si>
+    <t>Observation.category:second.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.category:second.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.category:second.coding.system</t>
   </si>
   <si>
     <t>http://loinc.org</t>
   </si>
   <si>
-    <t>Observation.category:microbiology.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.category:microbiology.coding.code</t>
+    <t>Observation.category:second.coding.version</t>
+  </si>
+  <si>
+    <t>Observation.category:second.coding.code</t>
   </si>
   <si>
     <t>18725-2</t>
   </si>
   <si>
-    <t>Observation.category:microbiology.coding.display</t>
+    <t>Observation.category:second.coding.display</t>
   </si>
   <si>
     <t>Microbiology studies (set)</t>
   </si>
   <si>
-    <t>Observation.category:microbiology.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.category:microbiology.text</t>
-  </si>
-  <si>
-    <t>Observation.category:microbiologyCategory</t>
-  </si>
-  <si>
-    <t>microbiologyCategory</t>
+    <t>Observation.category:second.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.category:second.text</t>
+  </si>
+  <si>
+    <t>Observation.category:third</t>
+  </si>
+  <si>
+    <t>third</t>
   </si>
   <si>
     <t>このObservationに関する詳細分類、JP_MicrobiologyCategory_VSより選択する、任意項目</t>
@@ -959,40 +969,40 @@
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MicrobiologyCategory_VS</t>
   </si>
   <si>
-    <t>Observation.category:microbiologyCategory.id</t>
-  </si>
-  <si>
-    <t>Observation.category:microbiologyCategory.extension</t>
-  </si>
-  <si>
-    <t>Observation.category:microbiologyCategory.coding</t>
-  </si>
-  <si>
-    <t>Observation.category:microbiologyCategory.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.category:microbiologyCategory.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.category:microbiologyCategory.coding.system</t>
+    <t>Observation.category:third.id</t>
+  </si>
+  <si>
+    <t>Observation.category:third.extension</t>
+  </si>
+  <si>
+    <t>Observation.category:third.coding</t>
+  </si>
+  <si>
+    <t>Observation.category:third.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.category:third.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.category:third.coding.system</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_MicrobiologyCategory_CS</t>
   </si>
   <si>
-    <t>Observation.category:microbiologyCategory.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.category:microbiologyCategory.coding.code</t>
-  </si>
-  <si>
-    <t>Observation.category:microbiologyCategory.coding.display</t>
-  </si>
-  <si>
-    <t>Observation.category:microbiologyCategory.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.category:microbiologyCategory.text</t>
+    <t>Observation.category:third.coding.version</t>
+  </si>
+  <si>
+    <t>Observation.category:third.coding.code</t>
+  </si>
+  <si>
+    <t>Observation.category:third.coding.display</t>
+  </si>
+  <si>
+    <t>Observation.category:third.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.category:third.text</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -1181,7 +1191,7 @@
     <t>Observation.code.coding:jlac10.system</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.200119.4.504</t>
+    <t>http://medis.or.jp/CodeSystem/master-JLAC10-17digits</t>
   </si>
   <si>
     <t>Observation.code.coding:jlac10.version</t>
@@ -1487,10 +1497,7 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1532,7 +1539,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Common)
 </t>
   </si>
   <si>
@@ -1595,7 +1602,7 @@
     <t>どの値が「正常」と見なされるかを知ることは、特定の結果の意義を評価するのに役立つ。さまざまなコンテキストに対応するため複数の参照範囲を提供できる必要がある。</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
@@ -1759,7 +1766,7 @@
     <t>このObservationに関連する子リソースに関する情報。このObservationに関連する/属するパネル検査や検査セットなどのObservationグループ</t>
   </si>
   <si>
-    <t>この要素を使用する場合、observationには通常、値または関連するリソースのセットのいじれかを含む。その両方を含む場合もある。複数のobservationをグループに一緒にまとめる方法については、以下の[メモ]（observation.html＃obsgrouping）を参照せよ。システムは、[QuestionnaireResponse]（questionnaireresponse.html）からの結果を計算して最終スコアにし、そのスコアをobservationとして表す場合があることに注意。</t>
+    <t>この要素を使用する場合、observationには通常、値または関連するリソースのセットのいずれかを含む。その両方を含む場合もある。複数のobservationをグループに一緒にまとめる方法については、以下の[メモ]（observation.html＃obsgrouping）を参照せよ。システムは、[QuestionnaireResponse]（questionnaireresponse.html）からの結果を計算して最終スコアにし、そのスコアをobservationとして表す場合があることに注意。</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>
@@ -2194,9 +2201,9 @@
   <dimension ref="A1:AP115"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="60.98046875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="53.97265625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="21.2734375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="17.9453125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2219,7 +2226,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="105.8828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="69.40234375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="66.27734375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -3996,22 +4003,24 @@
       <c r="X15" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="Y15" s="2"/>
+      <c r="Y15" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>188</v>
@@ -4038,10 +4047,10 @@
         <v>83</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>83</v>
@@ -4049,13 +4058,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>188</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>83</v>
@@ -4065,7 +4074,7 @@
         <v>94</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>83</v>
@@ -4080,13 +4089,13 @@
         <v>190</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O16" t="s" s="2">
         <v>193</v>
@@ -4118,7 +4127,7 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -4160,10 +4169,10 @@
         <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>83</v>
@@ -4171,10 +4180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4197,13 +4206,13 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4254,7 +4263,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4278,7 +4287,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4289,10 +4298,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4321,7 +4330,7 @@
         <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>143</v>
@@ -4362,19 +4371,19 @@
         <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4398,7 +4407,7 @@
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
@@ -4409,10 +4418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4435,19 +4444,19 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4496,7 +4505,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4517,10 +4526,10 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4531,10 +4540,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4557,13 +4566,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4614,7 +4623,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4638,7 +4647,7 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4649,10 +4658,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4681,7 +4690,7 @@
         <v>141</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>143</v>
@@ -4722,19 +4731,19 @@
         <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4758,7 +4767,7 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4769,10 +4778,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4798,23 +4807,23 @@
         <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>83</v>
@@ -4856,7 +4865,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4877,10 +4886,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4891,10 +4900,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4917,16 +4926,16 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4976,7 +4985,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4997,10 +5006,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -5011,10 +5020,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5040,21 +5049,21 @@
         <v>114</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>200</v>
+        <v>255</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -5096,7 +5105,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -5117,10 +5126,10 @@
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
@@ -5131,10 +5140,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5157,17 +5166,17 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -5216,7 +5225,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5237,10 +5246,10 @@
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
@@ -5251,10 +5260,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5277,19 +5286,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5338,7 +5347,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5359,10 +5368,10 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
@@ -5373,10 +5382,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5399,19 +5408,19 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5460,7 +5469,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5481,10 +5490,10 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
@@ -5495,13 +5504,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>188</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>83</v>
@@ -5526,13 +5535,13 @@
         <v>190</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>202</v>
+        <v>289</v>
       </c>
       <c r="O28" t="s" s="2">
         <v>193</v>
@@ -5562,9 +5571,11 @@
       <c r="X28" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="Y28" s="2"/>
+      <c r="Y28" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="Z28" t="s" s="2">
-        <v>286</v>
+        <v>195</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5606,10 +5617,10 @@
         <v>83</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>83</v>
@@ -5617,10 +5628,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5643,13 +5654,13 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5700,7 +5711,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5724,7 +5735,7 @@
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -5735,10 +5746,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5767,7 +5778,7 @@
         <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>143</v>
@@ -5808,19 +5819,19 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5844,7 +5855,7 @@
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -5855,10 +5866,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5881,19 +5892,19 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -5942,7 +5953,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5963,10 +5974,10 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -5977,10 +5988,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6003,13 +6014,13 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6060,7 +6071,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6084,7 +6095,7 @@
         <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -6095,10 +6106,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6127,7 +6138,7 @@
         <v>141</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>143</v>
@@ -6168,19 +6179,19 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6204,7 +6215,7 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6215,10 +6226,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6244,23 +6255,23 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -6302,7 +6313,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6323,10 +6334,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6337,10 +6348,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6363,16 +6374,16 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6422,7 +6433,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6443,10 +6454,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6457,10 +6468,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6486,21 +6497,21 @@
         <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -6542,7 +6553,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6563,10 +6574,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6577,10 +6588,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6603,17 +6614,17 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6623,7 +6634,7 @@
         <v>83</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>83</v>
@@ -6662,7 +6673,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6683,10 +6694,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6697,10 +6708,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6723,19 +6734,19 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6784,7 +6795,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6805,10 +6816,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -6819,10 +6830,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6845,19 +6856,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -6906,7 +6917,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6927,10 +6938,10 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
@@ -6941,13 +6952,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>188</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>83</v>
@@ -6972,13 +6983,13 @@
         <v>190</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>202</v>
+        <v>289</v>
       </c>
       <c r="O40" t="s" s="2">
         <v>193</v>
@@ -7010,7 +7021,7 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -7052,10 +7063,10 @@
         <v>83</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>83</v>
@@ -7063,10 +7074,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7089,13 +7100,13 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7146,7 +7157,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7170,7 +7181,7 @@
         <v>83</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
@@ -7181,10 +7192,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7213,7 +7224,7 @@
         <v>141</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>143</v>
@@ -7254,19 +7265,19 @@
         <v>83</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7290,7 +7301,7 @@
         <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -7301,10 +7312,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7327,19 +7338,19 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7388,7 +7399,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7409,10 +7420,10 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7423,10 +7434,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7449,13 +7460,13 @@
         <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7506,7 +7517,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7530,7 +7541,7 @@
         <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7541,10 +7552,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7573,7 +7584,7 @@
         <v>141</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>143</v>
@@ -7614,19 +7625,19 @@
         <v>83</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7650,7 +7661,7 @@
         <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -7661,10 +7672,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7690,23 +7701,23 @@
         <v>108</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>83</v>
@@ -7748,7 +7759,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7769,10 +7780,10 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7783,10 +7794,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7809,16 +7820,16 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7868,7 +7879,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7889,10 +7900,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7903,10 +7914,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7932,14 +7943,14 @@
         <v>114</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7988,7 +7999,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8009,10 +8020,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -8023,10 +8034,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8049,17 +8060,17 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -8108,7 +8119,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8129,10 +8140,10 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -8143,10 +8154,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8169,19 +8180,19 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8230,7 +8241,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8251,10 +8262,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8265,10 +8276,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8291,19 +8302,19 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8352,7 +8363,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8373,10 +8384,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8387,14 +8398,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8416,16 +8427,16 @@
         <v>190</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8450,13 +8461,13 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8474,7 +8485,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>94</v>
@@ -8489,30 +8500,30 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8535,13 +8546,13 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8592,7 +8603,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8616,7 +8627,7 @@
         <v>83</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -8627,10 +8638,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8659,7 +8670,7 @@
         <v>141</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>143</v>
@@ -8700,19 +8711,19 @@
         <v>83</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8736,7 +8747,7 @@
         <v>83</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8747,10 +8758,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8773,19 +8784,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8822,17 +8833,17 @@
         <v>83</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="AC55" s="2"/>
       <c r="AD55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8853,10 +8864,10 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8867,13 +8878,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="B56" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="B56" t="s" s="2">
-        <v>333</v>
-      </c>
       <c r="C56" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>83</v>
@@ -8895,19 +8906,19 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -8936,7 +8947,7 @@
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>83</v>
@@ -8954,7 +8965,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8975,10 +8986,10 @@
         <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -8989,10 +9000,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9015,13 +9026,13 @@
         <v>83</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9072,7 +9083,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9096,7 +9107,7 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -9107,10 +9118,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9139,7 +9150,7 @@
         <v>141</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>143</v>
@@ -9180,19 +9191,19 @@
         <v>83</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9216,7 +9227,7 @@
         <v>83</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
@@ -9227,10 +9238,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9256,23 +9267,23 @@
         <v>108</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="S59" t="s" s="2">
         <v>83</v>
@@ -9314,7 +9325,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9335,10 +9346,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9349,10 +9360,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9375,16 +9386,16 @@
         <v>95</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9434,7 +9445,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9455,10 +9466,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9469,10 +9480,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9498,14 +9509,14 @@
         <v>114</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9554,7 +9565,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9575,10 +9586,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9589,10 +9600,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9615,17 +9626,17 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9674,7 +9685,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9695,10 +9706,10 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9709,10 +9720,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9735,19 +9746,19 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9796,7 +9807,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9817,10 +9828,10 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9831,13 +9842,13 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>83</v>
@@ -9859,19 +9870,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9900,7 +9911,7 @@
       </c>
       <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>83</v>
@@ -9918,7 +9929,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9939,10 +9950,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9953,10 +9964,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9979,13 +9990,13 @@
         <v>83</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10036,7 +10047,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10060,7 +10071,7 @@
         <v>83</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -10071,10 +10082,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10103,7 +10114,7 @@
         <v>141</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>143</v>
@@ -10144,19 +10155,19 @@
         <v>83</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10180,7 +10191,7 @@
         <v>83</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -10191,10 +10202,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10220,23 +10231,23 @@
         <v>108</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>83</v>
@@ -10278,7 +10289,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10299,10 +10310,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10313,10 +10324,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10339,16 +10350,16 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10398,7 +10409,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10419,10 +10430,10 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10433,10 +10444,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10462,14 +10473,14 @@
         <v>114</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10518,7 +10529,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10539,10 +10550,10 @@
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>
@@ -10553,10 +10564,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10579,17 +10590,17 @@
         <v>95</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10638,7 +10649,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10659,10 +10670,10 @@
         <v>83</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
@@ -10673,10 +10684,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10699,19 +10710,19 @@
         <v>95</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10760,7 +10771,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10781,10 +10792,10 @@
         <v>83</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -10795,13 +10806,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D72" t="s" s="2">
         <v>83</v>
@@ -10823,19 +10834,19 @@
         <v>95</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10864,7 +10875,7 @@
       </c>
       <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -10882,7 +10893,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10903,10 +10914,10 @@
         <v>83</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
@@ -10917,10 +10928,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10943,13 +10954,13 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11000,7 +11011,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11024,7 +11035,7 @@
         <v>83</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -11035,10 +11046,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11067,7 +11078,7 @@
         <v>141</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>143</v>
@@ -11108,19 +11119,19 @@
         <v>83</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11144,7 +11155,7 @@
         <v>83</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
@@ -11155,10 +11166,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11184,23 +11195,23 @@
         <v>108</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q75" s="2"/>
       <c r="R75" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="S75" t="s" s="2">
         <v>83</v>
@@ -11242,7 +11253,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11263,10 +11274,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
@@ -11277,10 +11288,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11303,16 +11314,16 @@
         <v>95</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11362,7 +11373,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11383,10 +11394,10 @@
         <v>83</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
@@ -11397,10 +11408,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11426,14 +11437,14 @@
         <v>114</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>83</v>
@@ -11482,7 +11493,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11503,10 +11514,10 @@
         <v>83</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>83</v>
@@ -11517,10 +11528,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11543,17 +11554,17 @@
         <v>95</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>83</v>
@@ -11602,7 +11613,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11623,10 +11634,10 @@
         <v>83</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -11637,10 +11648,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11663,19 +11674,19 @@
         <v>95</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>83</v>
@@ -11724,7 +11735,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11745,10 +11756,10 @@
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -11759,10 +11770,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11785,19 +11796,19 @@
         <v>95</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>83</v>
@@ -11846,7 +11857,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -11867,10 +11878,10 @@
         <v>83</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>83</v>
@@ -11881,10 +11892,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11907,19 +11918,19 @@
         <v>95</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
@@ -11968,7 +11979,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -11983,19 +11994,19 @@
         <v>106</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>83</v>
@@ -12003,10 +12014,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12029,16 +12040,16 @@
         <v>95</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12088,7 +12099,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12109,13 +12120,13 @@
         <v>83</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>83</v>
@@ -12123,14 +12134,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12149,19 +12160,19 @@
         <v>95</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>83</v>
@@ -12210,7 +12221,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12225,19 +12236,19 @@
         <v>106</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>83</v>
@@ -12245,14 +12256,14 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12271,19 +12282,19 @@
         <v>95</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -12332,7 +12343,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12347,19 +12358,19 @@
         <v>106</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>83</v>
@@ -12367,10 +12378,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12393,16 +12404,16 @@
         <v>95</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12452,7 +12463,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12473,13 +12484,13 @@
         <v>83</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>83</v>
@@ -12487,10 +12498,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12513,19 +12524,19 @@
         <v>95</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -12574,7 +12585,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12589,19 +12600,19 @@
         <v>106</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>83</v>
@@ -12609,10 +12620,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12635,19 +12646,19 @@
         <v>95</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
@@ -12696,7 +12707,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12705,7 +12716,7 @@
         <v>94</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>106</v>
@@ -12714,27 +12725,27 @@
         <v>83</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12760,16 +12771,16 @@
         <v>190</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>83</v>
@@ -12794,13 +12805,13 @@
         <v>83</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>83</v>
@@ -12818,7 +12829,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12827,7 +12838,7 @@
         <v>94</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>106</v>
@@ -12842,7 +12853,7 @@
         <v>137</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -12853,14 +12864,14 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -12882,16 +12893,16 @@
         <v>190</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>83</v>
@@ -12916,13 +12927,13 @@
         <v>83</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>83</v>
@@ -12940,7 +12951,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -12958,27 +12969,27 @@
         <v>83</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13001,19 +13012,19 @@
         <v>83</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -13062,7 +13073,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13083,10 +13094,10 @@
         <v>83</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
@@ -13097,10 +13108,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13126,13 +13137,13 @@
         <v>190</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13158,31 +13169,29 @@
         <v>83</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="Y91" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="Y91" s="2"/>
+      <c r="Z91" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF91" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13200,27 +13209,27 @@
         <v>83</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13246,16 +13255,16 @@
         <v>190</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
@@ -13280,13 +13289,13 @@
         <v>83</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>83</v>
@@ -13304,7 +13313,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13325,10 +13334,10 @@
         <v>83</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
@@ -13339,10 +13348,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13365,16 +13374,16 @@
         <v>83</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13424,7 +13433,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13442,27 +13451,27 @@
         <v>83</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13485,16 +13494,16 @@
         <v>83</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13544,7 +13553,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13562,27 +13571,27 @@
         <v>83</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13605,19 +13614,19 @@
         <v>83</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -13666,7 +13675,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13678,7 +13687,7 @@
         <v>83</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>83</v>
@@ -13687,10 +13696,10 @@
         <v>83</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>83</v>
@@ -13701,10 +13710,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13727,13 +13736,13 @@
         <v>83</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13784,7 +13793,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -13808,7 +13817,7 @@
         <v>83</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>83</v>
@@ -13819,10 +13828,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13851,7 +13860,7 @@
         <v>141</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>143</v>
@@ -13904,7 +13913,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -13928,7 +13937,7 @@
         <v>83</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>83</v>
@@ -13939,14 +13948,14 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -13968,10 +13977,10 @@
         <v>140</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>143</v>
@@ -14026,7 +14035,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14061,10 +14070,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14087,13 +14096,13 @@
         <v>83</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14144,7 +14153,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14153,7 +14162,7 @@
         <v>94</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>106</v>
@@ -14165,10 +14174,10 @@
         <v>83</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>83</v>
@@ -14179,10 +14188,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14205,13 +14214,13 @@
         <v>83</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14262,7 +14271,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -14271,7 +14280,7 @@
         <v>94</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>106</v>
@@ -14283,10 +14292,10 @@
         <v>83</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>83</v>
@@ -14297,10 +14306,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14326,16 +14335,16 @@
         <v>190</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>83</v>
@@ -14363,10 +14372,10 @@
         <v>118</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>83</v>
@@ -14384,7 +14393,7 @@
         <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -14402,13 +14411,13 @@
         <v>83</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>83</v>
@@ -14419,10 +14428,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14448,16 +14457,16 @@
         <v>190</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>83</v>
@@ -14482,13 +14491,13 @@
         <v>83</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>83</v>
@@ -14506,7 +14515,7 @@
         <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -14524,13 +14533,13 @@
         <v>83</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>83</v>
@@ -14541,10 +14550,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14567,17 +14576,17 @@
         <v>83</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>83</v>
@@ -14626,7 +14635,7 @@
         <v>83</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -14650,7 +14659,7 @@
         <v>83</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>83</v>
@@ -14661,10 +14670,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14687,13 +14696,13 @@
         <v>83</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14744,7 +14753,7 @@
         <v>83</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -14765,10 +14774,10 @@
         <v>83</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>83</v>
@@ -14779,10 +14788,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14805,16 +14814,16 @@
         <v>95</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14864,7 +14873,7 @@
         <v>83</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -14885,10 +14894,10 @@
         <v>83</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>83</v>
@@ -14899,10 +14908,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14925,16 +14934,16 @@
         <v>95</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14984,7 +14993,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -15005,10 +15014,10 @@
         <v>83</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>83</v>
@@ -15019,10 +15028,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15045,19 +15054,19 @@
         <v>95</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>83</v>
@@ -15106,7 +15115,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15127,10 +15136,10 @@
         <v>83</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>83</v>
@@ -15141,10 +15150,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15167,13 +15176,13 @@
         <v>83</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15224,7 +15233,7 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -15248,7 +15257,7 @@
         <v>83</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>83</v>
@@ -15259,10 +15268,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15291,7 +15300,7 @@
         <v>141</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N109" t="s" s="2">
         <v>143</v>
@@ -15344,7 +15353,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -15368,7 +15377,7 @@
         <v>83</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>83</v>
@@ -15379,14 +15388,14 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15408,10 +15417,10 @@
         <v>140</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="N110" t="s" s="2">
         <v>143</v>
@@ -15466,7 +15475,7 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -15501,10 +15510,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15530,16 +15539,16 @@
         <v>190</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>83</v>
@@ -15564,13 +15573,13 @@
         <v>83</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>83</v>
@@ -15588,7 +15597,7 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>94</v>
@@ -15606,16 +15615,16 @@
         <v>83</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="AP111" t="s" s="2">
         <v>83</v>
@@ -15623,10 +15632,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15649,19 +15658,19 @@
         <v>95</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>83</v>
@@ -15710,7 +15719,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -15728,27 +15737,27 @@
         <v>83</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15774,16 +15783,16 @@
         <v>190</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>83</v>
@@ -15808,13 +15817,13 @@
         <v>83</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>83</v>
@@ -15832,7 +15841,7 @@
         <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -15841,7 +15850,7 @@
         <v>94</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>106</v>
@@ -15856,7 +15865,7 @@
         <v>137</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>83</v>
@@ -15867,14 +15876,14 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
@@ -15896,16 +15905,16 @@
         <v>190</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>83</v>
@@ -15930,13 +15939,13 @@
         <v>83</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>83</v>
@@ -15954,7 +15963,7 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -15972,27 +15981,27 @@
         <v>83</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16018,16 +16027,16 @@
         <v>84</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>83</v>
@@ -16076,7 +16085,7 @@
         <v>83</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -16097,10 +16106,10 @@
         <v>83</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/main/StructureDefinition-jp-observation-microbiology.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-microbiology.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/StructureDefinition-jp-observation-microbiology.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-microbiology.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4445" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4446" uniqueCount="603">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -283,7 +283,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReasonは、Observation.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:Observation.codeがObservation.component.codeと同じ場合、そのcodeに関連付くvalueは存在してはならない。 / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1416,7 +1416,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>結果（ `balue.value [x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
+    <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
@@ -1497,7 +1497,10 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
+    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1603,7 +1606,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
+obs-3:少なくともlow, high, textのいずれかが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
     <t>OBX.7</t>
@@ -1674,7 +1677,7 @@
     <t>Observation.referenceRange.type</t>
   </si>
   <si>
-    <t>参照範囲予選 / Reference range qualifier</t>
+    <t>参照範囲予選修飾子 / Reference range qualifier</t>
   </si>
   <si>
     <t>適用されるターゲット参照母集団のどの部分を示すコード。たとえば、通常または治療範囲。 / Codes to indicate the what part of the targeted reference population it applies to. For example, the normal or therapeutic range.</t>
@@ -1863,7 +1866,7 @@
   </si>
   <si>
     <t>「null」または例外的な値は、FHIR観測で2つの方法を表すことができます。1つの方法は、それらを単に値セットに含めるだけで、値の例外を表すことです。たとえば、血清学テストの測定値は、「検出」、「検出されない」、「決定的でない」、または「テストなし」です。
-別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、DataBsentrasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
+別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、dataAbsentReasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
 The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
   </si>
   <si>
@@ -2225,7 +2228,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="105.8828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="111.37890625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="66.27734375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -13171,9 +13174,11 @@
       <c r="X91" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="Y91" s="2"/>
+      <c r="Y91" t="s" s="2">
+        <v>476</v>
+      </c>
       <c r="Z91" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>83</v>
@@ -13209,27 +13214,27 @@
         <v>83</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13255,16 +13260,16 @@
         <v>190</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
@@ -13292,10 +13297,10 @@
         <v>325</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>83</v>
@@ -13313,7 +13318,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13334,10 +13339,10 @@
         <v>83</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
@@ -13348,10 +13353,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13374,16 +13379,16 @@
         <v>83</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13433,7 +13438,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13451,27 +13456,27 @@
         <v>83</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13494,16 +13499,16 @@
         <v>83</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13553,7 +13558,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13571,27 +13576,27 @@
         <v>83</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13614,19 +13619,19 @@
         <v>83</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -13675,7 +13680,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13687,7 +13692,7 @@
         <v>83</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>83</v>
@@ -13696,10 +13701,10 @@
         <v>83</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>83</v>
@@ -13710,10 +13715,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13828,10 +13833,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13948,14 +13953,14 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -13977,10 +13982,10 @@
         <v>140</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>143</v>
@@ -14035,7 +14040,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14070,10 +14075,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14096,13 +14101,13 @@
         <v>83</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14153,7 +14158,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14162,7 +14167,7 @@
         <v>94</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>106</v>
@@ -14174,10 +14179,10 @@
         <v>83</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>83</v>
@@ -14188,10 +14193,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14214,13 +14219,13 @@
         <v>83</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14271,7 +14276,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -14280,7 +14285,7 @@
         <v>94</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>106</v>
@@ -14292,10 +14297,10 @@
         <v>83</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>83</v>
@@ -14306,10 +14311,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14335,16 +14340,16 @@
         <v>190</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>83</v>
@@ -14372,10 +14377,10 @@
         <v>118</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>83</v>
@@ -14393,7 +14398,7 @@
         <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -14411,10 +14416,10 @@
         <v>83</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>464</v>
@@ -14428,10 +14433,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14457,16 +14462,16 @@
         <v>190</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>83</v>
@@ -14494,10 +14499,10 @@
         <v>325</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>83</v>
@@ -14515,7 +14520,7 @@
         <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -14533,10 +14538,10 @@
         <v>83</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>464</v>
@@ -14550,10 +14555,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14576,17 +14581,17 @@
         <v>83</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>83</v>
@@ -14635,7 +14640,7 @@
         <v>83</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -14659,7 +14664,7 @@
         <v>83</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>83</v>
@@ -14670,10 +14675,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14699,10 +14704,10 @@
         <v>207</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14753,7 +14758,7 @@
         <v>83</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -14774,10 +14779,10 @@
         <v>83</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>83</v>
@@ -14788,10 +14793,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14814,16 +14819,16 @@
         <v>95</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14873,7 +14878,7 @@
         <v>83</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -14894,10 +14899,10 @@
         <v>83</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>83</v>
@@ -14908,10 +14913,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14934,16 +14939,16 @@
         <v>95</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14993,7 +14998,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -15014,10 +15019,10 @@
         <v>83</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>83</v>
@@ -15028,10 +15033,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15054,19 +15059,19 @@
         <v>95</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>83</v>
@@ -15115,7 +15120,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15136,10 +15141,10 @@
         <v>83</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>83</v>
@@ -15150,10 +15155,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15268,10 +15273,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15388,14 +15393,14 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15417,10 +15422,10 @@
         <v>140</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N110" t="s" s="2">
         <v>143</v>
@@ -15475,7 +15480,7 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -15510,10 +15515,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15539,13 +15544,13 @@
         <v>190</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="O111" t="s" s="2">
         <v>324</v>
@@ -15597,7 +15602,7 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>94</v>
@@ -15615,7 +15620,7 @@
         <v>83</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>330</v>
@@ -15632,10 +15637,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15658,16 +15663,16 @@
         <v>95</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="O112" t="s" s="2">
         <v>440</v>
@@ -15719,7 +15724,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -15737,7 +15742,7 @@
         <v>83</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>443</v>
@@ -15754,10 +15759,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15783,13 +15788,13 @@
         <v>190</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="O113" t="s" s="2">
         <v>449</v>
@@ -15841,7 +15846,7 @@
         <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -15876,10 +15881,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15905,16 +15910,16 @@
         <v>190</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>83</v>
@@ -15963,7 +15968,7 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -15998,10 +16003,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16027,16 +16032,16 @@
         <v>84</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>83</v>
@@ -16085,7 +16090,7 @@
         <v>83</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -16106,10 +16111,10 @@
         <v>83</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/main/StructureDefinition-jp-observation-microbiology.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-microbiology.xlsx
@@ -2204,15 +2204,15 @@
   <dimension ref="A1:AP115"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="53.97265625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="17.9453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="46.2734375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="15.38671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2223,28 +2223,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="111.37890625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="66.27734375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="41.01953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="95.48828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.82421875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/main/StructureDefinition-jp-observation-microbiology.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-microbiology.xlsx
@@ -384,7 +384,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -625,7 +625,7 @@
     <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -1027,7 +1027,7 @@
     <t>単純な観測の名前を識別するコード。 / Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1240,7 +1240,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1419,7 +1419,7 @@
     <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1448,7 +1448,7 @@
     <t>観測の解釈を識別するコード。 / Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1500,7 +1500,7 @@
     <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1530,7 +1530,7 @@
     <t>単純な観測の方法。 / Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1567,7 +1567,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1642,7 +1642,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1692,7 +1692,7 @@
     <t>参照範囲の意味のコード。 / Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1725,7 +1725,7 @@
     <t>参照範囲が適用される母集団を識別するコード。 / Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>

--- a/jpcore-r4/main/StructureDefinition-jp-observation-microbiology.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-microbiology.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright JED-Project、JAHIS、日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG  
+    <t>Copyright JED-Project、JAHIS、一般社団法人日本医療情報学会FHIR国内実装基盤研究会  
 This material contains content from LOINC (http://loinc.org). LOINC is copyright © 1995+, Regenstrief Institute, Inc. and the Logical Observation Identifiers Names and Codes (LOINC) Committee and is available at no cost under the license at http://loinc.org/license. LOINC® is a registered United States trademark of Regenstrief Institute, Inc</t>
   </si>
   <si>
